--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20034685</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW CHO 100</t>
+    <t>20094328</t>
+  </si>
+  <si>
+    <t>PIATTOS SMB GPREK 65</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20034686</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW UBI 100</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20025762</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PNG 65G</t>
   </si>
   <si>
     <t>2</t>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094328</t>
-  </si>
-  <si>
-    <t>PIATTOS SMB GPREK 65</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,16 +28,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20025762</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PNG 65G</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20138272</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE SB 2X50</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
+  </si>
+  <si>
+    <t>20140018</t>
+  </si>
+  <si>
+    <t>IDM BB.WIPE RM 2X50S</t>
   </si>
 </sst>
 </file>
@@ -430,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -496,7 +511,47 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
+    <t>20129837</t>
+  </si>
+  <si>
+    <t>LARIST SPR.GRD 750ML</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,13 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20138272</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE SB 2X50</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20135849</t>
+  </si>
+  <si>
+    <t>LARIST SMR.BRZ 700ML</t>
+  </si>
+  <si>
+    <t>20081452</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 800</t>
   </si>
   <si>
     <t>2</t>
@@ -43,16 +49,52 @@
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20138273</t>
-  </si>
-  <si>
-    <t>LRST BB.WIPE AF 2X50</t>
-  </si>
-  <si>
-    <t>20140018</t>
-  </si>
-  <si>
-    <t>IDM BB.WIPE RM 2X50S</t>
+    <t>20084152</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW MLD C800</t>
+  </si>
+  <si>
+    <t>20087202</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 800</t>
+  </si>
+  <si>
+    <t>20140968</t>
+  </si>
+  <si>
+    <t>LFBUOY COOL FRS 800</t>
+  </si>
+  <si>
+    <t>20091870</t>
+  </si>
+  <si>
+    <t>SO KLN LIQ WH&amp;BR 510</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ SAKURA 510</t>
+  </si>
+  <si>
+    <t>20114428</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ KOREAN 510</t>
+  </si>
+  <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ LVNDR 510</t>
   </si>
 </sst>
 </file>
@@ -445,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -508,30 +550,30 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -548,10 +590,130 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129837</t>
-  </si>
-  <si>
-    <t>LARIST SPR.GRD 750ML</t>
+    <t>20060392</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CARING 400</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,73 +28,58 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20060393</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CLSC 400</t>
+  </si>
+  <si>
+    <t>20063269</t>
+  </si>
+  <si>
+    <t>NUVO CAIR NATURE 400</t>
+  </si>
+  <si>
+    <t>20114112</t>
+  </si>
+  <si>
+    <t>NUVO FRS.PRO LMN 400</t>
+  </si>
+  <si>
+    <t>20138658</t>
+  </si>
+  <si>
+    <t>NUVO BW HYGIENIC 400</t>
+  </si>
+  <si>
+    <t>20101378</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE PNK 50</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20121413</t>
+  </si>
+  <si>
+    <t>KDMO B.WP ALOE 2X50S</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20135849</t>
-  </si>
-  <si>
-    <t>LARIST SMR.BRZ 700ML</t>
-  </si>
-  <si>
-    <t>20081452</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 800</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20084152</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW MLD C800</t>
-  </si>
-  <si>
-    <t>20087202</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW LMN 800</t>
-  </si>
-  <si>
-    <t>20140968</t>
-  </si>
-  <si>
-    <t>LFBUOY COOL FRS 800</t>
-  </si>
-  <si>
-    <t>20091870</t>
-  </si>
-  <si>
-    <t>SO KLN LIQ WH&amp;BR 510</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ SAKURA 510</t>
-  </si>
-  <si>
-    <t>20114428</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ KOREAN 510</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ LVNDR 510</t>
   </si>
 </sst>
 </file>
@@ -487,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -570,18 +555,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -590,18 +575,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -610,27 +595,27 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -638,11 +623,11 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -650,70 +635,30 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t/>
   </si>
   <si>
-    <t>20060392</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CARING 400</t>
+    <t>20093221</t>
+  </si>
+  <si>
+    <t>INDOMIE GR AYM.GP 85</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,58 +28,40 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>20063269</t>
-  </si>
-  <si>
-    <t>NUVO CAIR NATURE 400</t>
-  </si>
-  <si>
-    <t>20114112</t>
-  </si>
-  <si>
-    <t>NUVO FRS.PRO LMN 400</t>
-  </si>
-  <si>
-    <t>20138658</t>
-  </si>
-  <si>
-    <t>NUVO BW HYGIENIC 400</t>
-  </si>
-  <si>
-    <t>20101378</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE PNK 50</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20101747</t>
+  </si>
+  <si>
+    <t>INDOMI SBLAK HOT/J75</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20121413</t>
-  </si>
-  <si>
-    <t>KDMO B.WP ALOE 2X50S</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
+    <t>20024079</t>
+  </si>
+  <si>
+    <t>TELUR AYM NEGERI BKL</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
   </si>
 </sst>
 </file>
@@ -472,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -575,7 +557,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -583,10 +565,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,70 +577,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMIE GR AYM.GP 85</t>
+    <t>20122975</t>
+  </si>
+  <si>
+    <t>CHOCOLITO RC.CHO 38G</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,40 +28,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20101747</t>
-  </si>
-  <si>
-    <t>INDOMI SBLAK HOT/J75</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>10040122</t>
+  </si>
+  <si>
+    <t>HISAMITSU KMPRS BABY</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20024079</t>
-  </si>
-  <si>
-    <t>TELUR AYM NEGERI BKL</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20130543</t>
+  </si>
+  <si>
+    <t>CHOCOLITO ORGNL 38G</t>
   </si>
 </sst>
 </file>
@@ -454,13 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -517,18 +502,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -537,50 +522,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t/>
   </si>
   <si>
-    <t>20122975</t>
-  </si>
-  <si>
-    <t>CHOCOLITO RC.CHO 38G</t>
+    <t>20001404</t>
+  </si>
+  <si>
+    <t>IDM HANDSOAP STW 375</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,25 +28,76 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20004027</t>
+  </si>
+  <si>
+    <t>IDM HANDSOAP CML 375</t>
+  </si>
+  <si>
+    <t>20092331</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ JR.NP650</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20107240</t>
+  </si>
+  <si>
+    <t>EKONOMI LIQ.SW&amp;JR650</t>
+  </si>
+  <si>
+    <t>20123812</t>
+  </si>
+  <si>
+    <t>EKONOMI LQ.SEREH 650</t>
+  </si>
+  <si>
+    <t>20135845</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ JR&amp;LMN650</t>
+  </si>
+  <si>
     <t>RT,(E-1.5B)</t>
   </si>
   <si>
-    <t>10040122</t>
-  </si>
-  <si>
-    <t>HISAMITSU KMPRS BABY</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20130543</t>
-  </si>
-  <si>
-    <t>CHOCOLITO ORGNL 38G</t>
+    <t>20136124</t>
+  </si>
+  <si>
+    <t>EKNOMI LIQ N&amp;JN 675G</t>
+  </si>
+  <si>
+    <t>20127573</t>
+  </si>
+  <si>
+    <t>LARISST PANTS ADL 8L</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20127575</t>
+  </si>
+  <si>
+    <t>LARISST PANTS ADL6XL</t>
+  </si>
+  <si>
+    <t>20127694</t>
+  </si>
+  <si>
+    <t>LARSST PANTS ADL 10M</t>
   </si>
 </sst>
 </file>
@@ -439,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -502,30 +553,170 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t/>
   </si>
   <si>
-    <t>20001404</t>
-  </si>
-  <si>
-    <t>IDM HANDSOAP STW 375</t>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,76 +28,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20004027</t>
-  </si>
-  <si>
-    <t>IDM HANDSOAP CML 375</t>
-  </si>
-  <si>
-    <t>20092331</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ JR.NP650</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20107240</t>
-  </si>
-  <si>
-    <t>EKONOMI LIQ.SW&amp;JR650</t>
-  </si>
-  <si>
-    <t>20123812</t>
-  </si>
-  <si>
-    <t>EKONOMI LQ.SEREH 650</t>
-  </si>
-  <si>
-    <t>20135845</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ JR&amp;LMN650</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20136124</t>
-  </si>
-  <si>
-    <t>EKNOMI LIQ N&amp;JN 675G</t>
-  </si>
-  <si>
-    <t>20127573</t>
-  </si>
-  <si>
-    <t>LARISST PANTS ADL 8L</t>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
+  </si>
+  <si>
+    <t>20027167</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP400</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20127575</t>
-  </si>
-  <si>
-    <t>LARISST PANTS ADL6XL</t>
-  </si>
-  <si>
-    <t>20127694</t>
-  </si>
-  <si>
-    <t>LARSST PANTS ADL 10M</t>
+    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -490,13 +466,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -553,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -561,10 +537,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -573,18 +549,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -593,18 +569,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -613,18 +589,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -633,18 +609,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -653,70 +629,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
+    <t>20054747</t>
+  </si>
+  <si>
+    <t>SO KLIN VL/BLSOM 700</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -31,49 +31,55 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>20046548</t>
+  </si>
+  <si>
+    <t>SOKLIN SOFT CAIR 700</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
-  </si>
-  <si>
-    <t>20027167</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP400</t>
+    <t>20067585</t>
+  </si>
+  <si>
+    <t>SOKLN LIQ RED SB 700</t>
+  </si>
+  <si>
+    <t>20137791</t>
+  </si>
+  <si>
+    <t>SO KLIN LIQ HJB 700</t>
+  </si>
+  <si>
+    <t>20039728</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 380ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20039727</t>
+  </si>
+  <si>
+    <t>SHINZU'I MATSU 380ML</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20130653</t>
+  </si>
+  <si>
+    <t>SHINZU'I SKURA 380ML</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -589,18 +595,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -609,18 +615,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -632,7 +638,7 @@
         <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20054747</t>
-  </si>
-  <si>
-    <t>SO KLIN VL/BLSOM 700</t>
+    <t>20060392</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CARING 400</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -31,55 +31,43 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20046548</t>
-  </si>
-  <si>
-    <t>SOKLIN SOFT CAIR 700</t>
+    <t>20060393</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CLSC 400</t>
+  </si>
+  <si>
+    <t>20063269</t>
+  </si>
+  <si>
+    <t>NUVO CAIR NATURE 400</t>
+  </si>
+  <si>
+    <t>20138658</t>
+  </si>
+  <si>
+    <t>NUVO BW HYGIENIC 400</t>
+  </si>
+  <si>
+    <t>20114112</t>
+  </si>
+  <si>
+    <t>NUVO FRS.PRO LMN 400</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20067585</t>
-  </si>
-  <si>
-    <t>SOKLN LIQ RED SB 700</t>
-  </si>
-  <si>
-    <t>20137791</t>
-  </si>
-  <si>
-    <t>SO KLIN LIQ HJB 700</t>
-  </si>
-  <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KIREI 380ML</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20039727</t>
-  </si>
-  <si>
-    <t>SHINZU'I MATSU 380ML</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKURA 380ML</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
+    <t>PT</t>
   </si>
 </sst>
 </file>
@@ -472,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -535,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -543,10 +531,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -555,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -563,10 +551,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -575,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -583,10 +571,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +583,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,30 +603,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
   <si>
     <t/>
   </si>
   <si>
-    <t>20060392</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CARING 400</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,46 +28,73 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20116823</t>
+  </si>
+  <si>
+    <t>CIPTADEN JB FRESH225</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>20063269</t>
-  </si>
-  <si>
-    <t>NUVO CAIR NATURE 400</t>
-  </si>
-  <si>
-    <t>20138658</t>
-  </si>
-  <si>
-    <t>NUVO BW HYGIENIC 400</t>
-  </si>
-  <si>
-    <t>20114112</t>
-  </si>
-  <si>
-    <t>NUVO FRS.PRO LMN 400</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
+    <t>20127600</t>
+  </si>
+  <si>
+    <t>CPTADEN JB C.MINT225</t>
+  </si>
+  <si>
+    <t>20060386</t>
+  </si>
+  <si>
+    <t>GIV BW MLB&amp;CLG PC400</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT</t>
+    <t>20073514</t>
+  </si>
+  <si>
+    <t>GIV BW FLW&amp;BER 400ML</t>
+  </si>
+  <si>
+    <t>20121017</t>
+  </si>
+  <si>
+    <t>GIV BW HJB SAF&amp;N 400</t>
+  </si>
+  <si>
+    <t>20138029</t>
+  </si>
+  <si>
+    <t>GIV BW SAKURA 400ML</t>
+  </si>
+  <si>
+    <t>20138875</t>
+  </si>
+  <si>
+    <t>GIV BW SF&amp;SM 400ML</t>
+  </si>
+  <si>
+    <t>20131788</t>
+  </si>
+  <si>
+    <t>MAMA LMN JR.NPS 950</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20142275</t>
+  </si>
+  <si>
+    <t>MAMA LIME CHARCO 950</t>
   </si>
 </sst>
 </file>
@@ -460,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -523,38 +550,38 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -563,18 +590,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -586,15 +613,15 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -603,10 +630,90 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t/>
   </si>
   <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
+    <t>20141345</t>
+  </si>
+  <si>
+    <t>LARISST S/PCC PRG650</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,73 +28,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20116823</t>
-  </si>
-  <si>
-    <t>CIPTADEN JB FRESH225</t>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20073425</t>
+  </si>
+  <si>
+    <t>IDM P.PRNG JRK.N 650</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20127600</t>
-  </si>
-  <si>
-    <t>CPTADEN JB C.MINT225</t>
-  </si>
-  <si>
-    <t>20060386</t>
-  </si>
-  <si>
-    <t>GIV BW MLB&amp;CLG PC400</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20073514</t>
-  </si>
-  <si>
-    <t>GIV BW FLW&amp;BER 400ML</t>
-  </si>
-  <si>
-    <t>20121017</t>
-  </si>
-  <si>
-    <t>GIV BW HJB SAF&amp;N 400</t>
-  </si>
-  <si>
-    <t>20138029</t>
-  </si>
-  <si>
-    <t>GIV BW SAKURA 400ML</t>
-  </si>
-  <si>
-    <t>20138875</t>
-  </si>
-  <si>
-    <t>GIV BW SF&amp;SM 400ML</t>
-  </si>
-  <si>
-    <t>20131788</t>
-  </si>
-  <si>
-    <t>MAMA LMN JR.NPS 950</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20142275</t>
-  </si>
-  <si>
-    <t>MAMA LIME CHARCO 950</t>
+    <t>20115958</t>
+  </si>
+  <si>
+    <t>GENTLE GEN PRS.G 700</t>
+  </si>
+  <si>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
+  </si>
+  <si>
+    <t>20133333</t>
+  </si>
+  <si>
+    <t>GENTLE GEN A/KRGT700</t>
+  </si>
+  <si>
+    <t>20141371</t>
+  </si>
+  <si>
+    <t>GNTLE GEN CMLLIA 700</t>
+  </si>
+  <si>
+    <t>20141372</t>
+  </si>
+  <si>
+    <t>GENTLE GEN LILAC 700</t>
   </si>
 </sst>
 </file>
@@ -487,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -553,47 +538,47 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -610,10 +595,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -630,10 +615,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -650,10 +635,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -670,50 +655,10 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141345</t>
-  </si>
-  <si>
-    <t>LARISST S/PCC PRG650</t>
+    <t>20124726</t>
+  </si>
+  <si>
+    <t>IDM F/T 2PLY 3X180'S</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,58 +28,31 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20073425</t>
-  </si>
-  <si>
-    <t>IDM P.PRNG JRK.N 650</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20042025</t>
+  </si>
+  <si>
+    <t>INDOCAFE MX 3IN1 10S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20115958</t>
-  </si>
-  <si>
-    <t>GENTLE GEN PRS.G 700</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>20133333</t>
-  </si>
-  <si>
-    <t>GENTLE GEN A/KRGT700</t>
-  </si>
-  <si>
-    <t>20141371</t>
-  </si>
-  <si>
-    <t>GNTLE GEN CMLLIA 700</t>
-  </si>
-  <si>
-    <t>20141372</t>
-  </si>
-  <si>
-    <t>GENTLE GEN LILAC 700</t>
+    <t>RT,(E-2B)</t>
   </si>
 </sst>
 </file>
@@ -472,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -538,15 +511,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -555,110 +528,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20124726</t>
-  </si>
-  <si>
-    <t>IDM F/T 2PLY 3X180'S</t>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND ST 189 ML</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,31 +28,46 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20042025</t>
-  </si>
-  <si>
-    <t>INDOCAFE MX 3IN1 10S</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CO 189 ML</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
+    <t>20122061</t>
+  </si>
+  <si>
+    <t>OATSDE O/M B/BL 1 L</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>20036590</t>
+  </si>
+  <si>
+    <t>LWK WHKO ORG 9x20 G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20073043</t>
+  </si>
+  <si>
+    <t>LWK WHKO LS 9x19 G</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -445,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -511,15 +526,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -528,10 +543,50 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND ST 189 ML</t>
+    <t>20115153</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE A/B50S</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -31,43 +31,46 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CO 189 ML</t>
+    <t>20138144</t>
+  </si>
+  <si>
+    <t>KODOMO WPS H&amp;M 2X50S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20122061</t>
-  </si>
-  <si>
-    <t>OATSDE O/M B/BL 1 L</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20141370</t>
+  </si>
+  <si>
+    <t>LISTERINE WTRMLN 250</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20036590</t>
-  </si>
-  <si>
-    <t>LWK WHKO ORG 9x20 G</t>
+    <t>10012742</t>
+  </si>
+  <si>
+    <t>LISTERINE COOLMIN250</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20073043</t>
-  </si>
-  <si>
-    <t>LWK WHKO LS 9x19 G</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>20067228</t>
+  </si>
+  <si>
+    <t>LISTERINE ZERO 250ML</t>
+  </si>
+  <si>
+    <t>20137312</t>
+  </si>
+  <si>
+    <t>LSTRNE SAKURA&amp;PC 250</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -526,15 +529,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -543,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -551,10 +554,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -563,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -583,10 +586,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t/>
   </si>
   <si>
-    <t>20115153</t>
-  </si>
-  <si>
-    <t>KODOMO B.WIPE A/B50S</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,49 +28,43 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138144</t>
-  </si>
-  <si>
-    <t>KODOMO WPS H&amp;M 2X50S</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20035113</t>
+  </si>
+  <si>
+    <t>MITU WIPE BLUE BB 40</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20141370</t>
-  </si>
-  <si>
-    <t>LISTERINE WTRMLN 250</t>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
+  </si>
+  <si>
+    <t>20001546</t>
+  </si>
+  <si>
+    <t>MITU TIS.G/P BLU2X50</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>10012742</t>
-  </si>
-  <si>
-    <t>LISTERINE COOLMIN250</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20067228</t>
-  </si>
-  <si>
-    <t>LISTERINE ZERO 250ML</t>
-  </si>
-  <si>
-    <t>20137312</t>
-  </si>
-  <si>
-    <t>LSTRNE SAKURA&amp;PC 250</t>
   </si>
 </sst>
 </file>
@@ -463,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -546,10 +540,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -566,7 +560,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
@@ -574,10 +568,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -586,30 +580,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
   <si>
     <t/>
   </si>
   <si>
-    <t>20027166</t>
-  </si>
-  <si>
-    <t>IDM FAC.TISSUE NP220</t>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,13 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20001061</t>
-  </si>
-  <si>
-    <t>MITU G/P PINK 2X50'S</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20091183</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT STR 6X110</t>
+  </si>
+  <si>
+    <t>10012172</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VNLA 230</t>
   </si>
   <si>
     <t>2</t>
@@ -43,28 +49,28 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20035113</t>
-  </si>
-  <si>
-    <t>MITU WIPE BLUE BB 40</t>
+    <t>10020147</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD CKLT 230</t>
+  </si>
+  <si>
+    <t>10033572</t>
+  </si>
+  <si>
+    <t>PEDIASURE VAN KLG800</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20071105</t>
-  </si>
-  <si>
-    <t>MITU GP PURPLE 2X50S</t>
-  </si>
-  <si>
-    <t>20001546</t>
-  </si>
-  <si>
-    <t>MITU TIS.G/P BLU2X50</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>20008081</t>
+  </si>
+  <si>
+    <t>PEDIASURE MDU.KLG800</t>
   </si>
 </sst>
 </file>
@@ -457,16 +463,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -485,8 +492,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -502,11 +515,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -520,18 +533,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -540,18 +553,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -560,18 +573,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -580,10 +593,30 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
+    <t>20042025</t>
+  </si>
+  <si>
+    <t>INDOCAFE MX 3IN1 10S</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,19 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20091183</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT STR 6X110</t>
-  </si>
-  <si>
-    <t>10012172</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VNLA 230</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20016512</t>
+  </si>
+  <si>
+    <t>SUNCO MNYK GORENG 2L</t>
   </si>
   <si>
     <t>2</t>
@@ -49,28 +43,13 @@
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>10020147</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD CKLT 230</t>
-  </si>
-  <si>
-    <t>10033572</t>
-  </si>
-  <si>
-    <t>PEDIASURE VAN KLG800</t>
+    <t>10010805</t>
+  </si>
+  <si>
+    <t>SANIA MNYK GR PCH 2L</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20008081</t>
-  </si>
-  <si>
-    <t>PEDIASURE MDU.KLG800</t>
   </si>
 </sst>
 </file>
@@ -463,17 +442,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,14 +470,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -515,11 +487,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -533,18 +505,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -553,70 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20042025</t>
-  </si>
-  <si>
-    <t>INDOCAFE MX 3IN1 10S</t>
+    <t>20091870</t>
+  </si>
+  <si>
+    <t>SKLN LQ WHT&amp;BRGHT500</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,25 +28,43 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20016512</t>
-  </si>
-  <si>
-    <t>SUNCO MNYK GORENG 2L</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20093627</t>
+  </si>
+  <si>
+    <t>SKLN LQD SKR STRW500</t>
+  </si>
+  <si>
+    <t>20114428</t>
+  </si>
+  <si>
+    <t>SKLN LQD KOR CMLA500</t>
+  </si>
+  <si>
+    <t>20123818</t>
+  </si>
+  <si>
+    <t>SKLN LQD PROV LVD500</t>
+  </si>
+  <si>
+    <t>20112491</t>
+  </si>
+  <si>
+    <t>SNLIGHT LIME PCH 910</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10010805</t>
-  </si>
-  <si>
-    <t>SANIA MNYK GR PCH 2L</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20139728</t>
+  </si>
+  <si>
+    <t>SNLGHT BIO BLBR 870G</t>
   </si>
   <si>
     <t>3</t>
@@ -442,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -505,18 +523,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +543,70 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t/>
   </si>
   <si>
-    <t>20091870</t>
-  </si>
-  <si>
-    <t>SKLN LQ WHT&amp;BRGHT500</t>
+    <t>20038763</t>
+  </si>
+  <si>
+    <t>PNTENE SHP ANT/D 145</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,46 +28,52 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20093627</t>
-  </si>
-  <si>
-    <t>SKLN LQD SKR STRW500</t>
-  </si>
-  <si>
-    <t>20114428</t>
-  </si>
-  <si>
-    <t>SKLN LQD KOR CMLA500</t>
-  </si>
-  <si>
-    <t>20123818</t>
-  </si>
-  <si>
-    <t>SKLN LQD PROV LVD500</t>
-  </si>
-  <si>
-    <t>20112491</t>
-  </si>
-  <si>
-    <t>SNLIGHT LIME PCH 910</t>
+    <t>PT,(E-5B)</t>
+  </si>
+  <si>
+    <t>20038766</t>
+  </si>
+  <si>
+    <t>PANTENE SHP HFC 145</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>20038986</t>
+  </si>
+  <si>
+    <t>PNTENE SHP LG BLK145</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20038758</t>
+  </si>
+  <si>
+    <t>PANTENE CND HFC 160</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20038770</t>
+  </si>
+  <si>
+    <t>PNTENE SHP SM.CR 145</t>
+  </si>
+  <si>
+    <t>20139653</t>
+  </si>
+  <si>
+    <t>LRST FAC.TIS 2X200S</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>PT</t>
-  </si>
-  <si>
-    <t>20139728</t>
-  </si>
-  <si>
-    <t>SNLGHT BIO BLBR 870G</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -531,10 +537,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -543,7 +549,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -551,10 +557,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -563,7 +569,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -571,10 +577,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -586,15 +592,15 @@
         <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -603,10 +609,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU3AMKT.xlsx
+++ b/E/DU3AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="26">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003974</t>
-  </si>
-  <si>
-    <t>TROPICAL MNYK BTL 2L</t>
+    <t>10003550</t>
+  </si>
+  <si>
+    <t>CIPTADENT FRS.MIN190</t>
   </si>
   <si>
     <t>DU3AMKT</t>
@@ -28,43 +28,67 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>10005838</t>
-  </si>
-  <si>
-    <t>FILMA MINYAK GR RF2L</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139068</t>
+  </si>
+  <si>
+    <t>CPTDENT FRESH MC 190</t>
+  </si>
+  <si>
+    <t>10004051</t>
+  </si>
+  <si>
+    <t>CIPTADENT COOL MN190</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20042991</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR PRM 1KG</t>
+    <t>20093188</t>
+  </si>
+  <si>
+    <t>RNSO MLT G.LQ 510 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20052296</t>
-  </si>
-  <si>
-    <t>IDM GULA PRM KNG 1KG</t>
-  </si>
-  <si>
-    <t>20139025</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 1KG</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20054750</t>
+  </si>
+  <si>
+    <t>RNSO LIQ PRFM 510 G</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20122879</t>
+  </si>
+  <si>
+    <t>RNSO MLT K STR 510 G</t>
+  </si>
+  <si>
+    <t>20140001</t>
+  </si>
+  <si>
+    <t>RNSO PURE LIQ 510 G</t>
+  </si>
+  <si>
+    <t>20137793</t>
+  </si>
+  <si>
+    <t>RNSO ROSE FRS 510 G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -457,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -520,7 +544,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -528,42 +552,42 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -580,10 +604,70 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
